--- a/data/ready_stocks/ad-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/ad-wb-stocks-updated.xlsx
@@ -476,7 +476,7 @@
         <v>2045411146747</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -484,7 +484,7 @@
         <v>2045411146785</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -500,7 +500,7 @@
         <v>2045411147263</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -564,7 +564,7 @@
         <v>2045411146914</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -620,7 +620,7 @@
         <v>2045411146877</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -628,7 +628,7 @@
         <v>2045411146853</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -676,7 +676,7 @@
         <v>2045411147454</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -740,7 +740,7 @@
         <v>2045411146471</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -764,7 +764,7 @@
         <v>2045411146921</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>2045411146945</v>
       </c>
       <c r="B59">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -972,7 +972,7 @@
         <v>2045411147560</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1044,7 +1044,7 @@
         <v>2045411146679</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1228,7 +1228,7 @@
         <v>2045413136395</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -1236,7 +1236,7 @@
         <v>2045413135855</v>
       </c>
       <c r="B105">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1276,7 +1276,7 @@
         <v>2045411146655</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1292,7 +1292,7 @@
         <v>2045413136098</v>
       </c>
       <c r="B112">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -1332,7 +1332,7 @@
         <v>2045413135800</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -1356,7 +1356,7 @@
         <v>2045413136333</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -1444,7 +1444,7 @@
         <v>2045411146600</v>
       </c>
       <c r="B131">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -1524,7 +1524,7 @@
         <v>2045411146556</v>
       </c>
       <c r="B141">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -1548,7 +1548,7 @@
         <v>2045413136470</v>
       </c>
       <c r="B144">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -1564,7 +1564,7 @@
         <v>2045413136418</v>
       </c>
       <c r="B146">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -1580,7 +1580,7 @@
         <v>2045413136142</v>
       </c>
       <c r="B148">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -1620,7 +1620,7 @@
         <v>2045413136425</v>
       </c>
       <c r="B153">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -1628,7 +1628,7 @@
         <v>2045413135909</v>
       </c>
       <c r="B154">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/ready_stocks/ad-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/ad-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B153"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,71 +409,71 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2045411146990</v>
+        <v>2045411147553</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>2045411147553</v>
+        <v>2045411146952</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2045411146952</v>
+        <v>2045411146860</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2045411146860</v>
+        <v>2045411147409</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2045411147409</v>
+        <v>2045411147348</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>2045411147348</v>
+        <v>2045411146693</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2045411146693</v>
+        <v>2045411146969</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2045411146969</v>
+        <v>2045411146747</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2045411146747</v>
+        <v>2045411146785</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -481,7 +481,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>2045411146785</v>
+        <v>2045411147027</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -489,15 +489,15 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>2045411147027</v>
+        <v>2045411147263</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2045411147263</v>
+        <v>2045411146303</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -505,39 +505,39 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>2045411146303</v>
+        <v>2045411146808</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>2045411146808</v>
+        <v>2045411146815</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>2045411146815</v>
+        <v>2045411147102</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>2045411147102</v>
+        <v>2045411146778</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>2045411146778</v>
+        <v>2045411147041</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -545,23 +545,23 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>2045411147041</v>
+        <v>2045411146259</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>2045411146259</v>
+        <v>2045411146914</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>2045411146914</v>
+        <v>2045411146709</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -569,55 +569,55 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>2045411146709</v>
+        <v>2045411146334</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>2045411146334</v>
+        <v>2045411147263</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>2045411147263</v>
+        <v>2045411146983</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>2045411146983</v>
+        <v>2045411147232</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>2045411147232</v>
+        <v>2045411147256</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>2045411147256</v>
+        <v>2045411146877</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>2045411146877</v>
+        <v>2045411146853</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>2045411146853</v>
+        <v>2045411146358</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -633,111 +633,111 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>2045411146358</v>
+        <v>2045411146716</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>2045411146716</v>
+        <v>2045411147423</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>2045411147423</v>
+        <v>2045411147010</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>2045411147010</v>
+        <v>2045411147065</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>2045411147065</v>
+        <v>2045411147454</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>2045411147454</v>
+        <v>2045411147140</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>2045411147140</v>
+        <v>2045411147058</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>2045411147058</v>
+        <v>2045411147478</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>2045411147478</v>
+        <v>2045411147164</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>2045411147164</v>
+        <v>2045411146372</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>2045411146372</v>
+        <v>2045411147447</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>2045411147447</v>
+        <v>2045411147126</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>2045411147126</v>
+        <v>2045411146471</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>2045411146471</v>
+        <v>2045411146907</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -745,23 +745,23 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2045411146907</v>
+        <v>2045411147089</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2045411147089</v>
+        <v>2045411146921</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2045411146921</v>
+        <v>2045411147034</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -769,39 +769,39 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>2045411147034</v>
+        <v>2045411147249</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>2045411147249</v>
+        <v>2045411146280</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2045411146280</v>
+        <v>2045411147157</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>2045411147157</v>
+        <v>2045411147218</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>2045411147218</v>
+        <v>2045411147492</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -809,63 +809,63 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>2045411147492</v>
+        <v>2045411146792</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>2045411146792</v>
+        <v>2045411147331</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>2045411147331</v>
+        <v>2045411146488</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>2045411146488</v>
+        <v>2045411146891</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>2045411146891</v>
+        <v>2045411147539</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>2045411147539</v>
+        <v>2045411147287</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>2045411147287</v>
+        <v>2045411146945</v>
       </c>
       <c r="B58">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>2045411146945</v>
+        <v>2045411147294</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -873,47 +873,47 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>2045411147294</v>
+        <v>2045411147591</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>2045411147591</v>
+        <v>2045411146754</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>2045411146754</v>
+        <v>2045411146938</v>
       </c>
       <c r="B62">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>2045411146938</v>
+        <v>2045411146846</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>2045411146846</v>
+        <v>2045411147645</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>2045411147645</v>
+        <v>2045411146662</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>2045411146662</v>
+        <v>2045411147546</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -929,47 +929,47 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>2045411147546</v>
+        <v>2045411146884</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>2045411146884</v>
+        <v>2045411147300</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>2045411147300</v>
+        <v>2045411147379</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>2045411147379</v>
+        <v>2045411146440</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>2045411146440</v>
+        <v>2045411147560</v>
       </c>
       <c r="B71">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>2045411147560</v>
+        <v>2045411147362</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -977,71 +977,71 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>2045411147362</v>
+        <v>2045411146686</v>
       </c>
       <c r="B73">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>2045411146686</v>
+        <v>2045411147430</v>
       </c>
       <c r="B74">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>2045411147430</v>
+        <v>2045411147119</v>
       </c>
       <c r="B75">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>2045411147119</v>
+        <v>2045411146822</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>2045411146822</v>
+        <v>2045411147393</v>
       </c>
       <c r="B77">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>2045411147393</v>
+        <v>2045411147096</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>2045411147096</v>
+        <v>2045411147201</v>
       </c>
       <c r="B79">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>2045411147201</v>
+        <v>2045411146679</v>
       </c>
       <c r="B80">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>2045411146679</v>
+        <v>2045411147133</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1049,135 +1049,135 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>2045411147133</v>
+        <v>2045411147270</v>
       </c>
       <c r="B82">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>2045411147270</v>
+        <v>2045411147324</v>
       </c>
       <c r="B83">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>2045411147324</v>
+        <v>2045411147614</v>
       </c>
       <c r="B84">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>2045411147614</v>
+        <v>2045411147461</v>
       </c>
       <c r="B85">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>2045411147461</v>
+        <v>2045411147072</v>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>2045411147072</v>
+        <v>2045411147485</v>
       </c>
       <c r="B87">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>2045411147485</v>
+        <v>2045411146761</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>2045411146761</v>
+        <v>2045411146402</v>
       </c>
       <c r="B89">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>2045411146402</v>
+        <v>2045411147577</v>
       </c>
       <c r="B90">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>2045411147577</v>
+        <v>2045411147065</v>
       </c>
       <c r="B91">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>2045411147065</v>
+        <v>2045411147621</v>
       </c>
       <c r="B92">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>2045411147621</v>
+        <v>2045411147416</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>2045411147416</v>
+        <v>2045411147508</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>2045411147508</v>
+        <v>2045411147584</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>2045411147584</v>
+        <v>2045411147386</v>
       </c>
       <c r="B96">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>2045411147386</v>
+        <v>2045411146723</v>
       </c>
       <c r="B97">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>2045411146723</v>
+        <v>2045411146730</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1185,47 +1185,47 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>2045411146730</v>
+        <v>2045411147355</v>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>2045411147355</v>
+        <v>2045411147317</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>2045411147317</v>
+        <v>2045411146617</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>2045411146617</v>
+        <v>2045411146631</v>
       </c>
       <c r="B102">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>2045411146631</v>
+        <v>2045413136395</v>
       </c>
       <c r="B103">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>2045413136395</v>
+        <v>2045413135855</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>2045413135855</v>
+        <v>2045413136494</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1241,39 +1241,39 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>2045413136494</v>
+        <v>2045413135893</v>
       </c>
       <c r="B106">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>2045413135893</v>
+        <v>2045411146563</v>
       </c>
       <c r="B107">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>2045411146563</v>
+        <v>2045411146648</v>
       </c>
       <c r="B108">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>2045411146648</v>
+        <v>2045411146655</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>2045411146655</v>
+        <v>2045411146594</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1281,15 +1281,15 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>2045411146594</v>
+        <v>2045413136098</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>2045413136098</v>
+        <v>2045413135817</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1297,47 +1297,47 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>2045413135817</v>
+        <v>2045411146495</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>2045411146495</v>
+        <v>2045411146570</v>
       </c>
       <c r="B114">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>2045411146570</v>
+        <v>2045413136371</v>
       </c>
       <c r="B115">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>2045413136371</v>
+        <v>2045413135800</v>
       </c>
       <c r="B116">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>2045413135800</v>
+        <v>2045413136081</v>
       </c>
       <c r="B117">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>2045413136081</v>
+        <v>2045413135848</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>2045413135848</v>
+        <v>2045413136333</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>2045413136333</v>
+        <v>2045413136463</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -1361,39 +1361,39 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>2045413136463</v>
+        <v>2045413136340</v>
       </c>
       <c r="B121">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>2045413136340</v>
+        <v>2045413136135</v>
       </c>
       <c r="B122">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>2045413136135</v>
+        <v>2045413135886</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>2045413135886</v>
+        <v>2045413135862</v>
       </c>
       <c r="B124">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>2045413135862</v>
+        <v>2045413136517</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>2045413136517</v>
+        <v>2045413136029</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>2045413136029</v>
+        <v>2045413136036</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -1417,31 +1417,31 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>2045413136036</v>
+        <v>2045413136449</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>2045413136449</v>
+        <v>2045411146518</v>
       </c>
       <c r="B129">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>2045411146518</v>
+        <v>2045411146600</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>2045411146600</v>
+        <v>2045413135824</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -1449,31 +1449,31 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>2045413135824</v>
+        <v>2045413136111</v>
       </c>
       <c r="B132">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>2045413136111</v>
+        <v>2045411146525</v>
       </c>
       <c r="B133">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>2045411146525</v>
+        <v>2045413136067</v>
       </c>
       <c r="B134">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>2045413136067</v>
+        <v>2045413136500</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1481,47 +1481,47 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>2045413136500</v>
+        <v>2045413135879</v>
       </c>
       <c r="B136">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>2045413135879</v>
+        <v>2045413136364</v>
       </c>
       <c r="B137">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>2045413136364</v>
+        <v>2045411146532</v>
       </c>
       <c r="B138">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>2045411146532</v>
+        <v>2045411146549</v>
       </c>
       <c r="B139">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>2045411146549</v>
+        <v>2045411146556</v>
       </c>
       <c r="B140">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>2045411146556</v>
+        <v>2045411146501</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1529,23 +1529,23 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>2045411146501</v>
+        <v>2045413136166</v>
       </c>
       <c r="B142">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>2045413136166</v>
+        <v>2045413136470</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>2045413136470</v>
+        <v>2045413136487</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>2045413136487</v>
+        <v>2045413136418</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>2045413136418</v>
+        <v>2045413136050</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1569,15 +1569,15 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>2045413136050</v>
+        <v>2045413136142</v>
       </c>
       <c r="B147">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>2045413136142</v>
+        <v>2045411146624</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1585,55 +1585,47 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>2045411146624</v>
+        <v>2045411146587</v>
       </c>
       <c r="B149">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>2045411146587</v>
+        <v>2045413136456</v>
       </c>
       <c r="B150">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>2045413136456</v>
+        <v>2045413136302</v>
       </c>
       <c r="B151">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>2045413136302</v>
+        <v>2045413136425</v>
       </c>
       <c r="B152">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>2045413136425</v>
+        <v>2045413135909</v>
       </c>
       <c r="B153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154">
-        <v>2045413135909</v>
-      </c>
-      <c r="B154">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B153"/>
   </ignoredErrors>
 </worksheet>
 </file>